--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N78_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N78_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.182841234407417</v>
+        <v>1.004711700591205</v>
       </c>
       <c r="D2" t="n">
-        <v>20.91946886939955</v>
+        <v>3.399413691277427</v>
       </c>
       <c r="E2" t="n">
-        <v>8.614494295719174</v>
+        <v>1.399855323054366</v>
       </c>
       <c r="F2" t="n">
-        <v>6.723054750622592</v>
+        <v>1.092496396976171</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.78145093060155</v>
+        <v>4.026985776222752</v>
       </c>
       <c r="D3" t="n">
-        <v>19.0501468590845</v>
+        <v>3.095648864601231</v>
       </c>
       <c r="E3" t="n">
-        <v>8.614494295719174</v>
+        <v>1.399855323054366</v>
       </c>
       <c r="F3" t="n">
-        <v>6.723054750622592</v>
+        <v>1.092496396976171</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.29140618330642</v>
+        <v>2.484853504787294</v>
       </c>
       <c r="D4" t="n">
-        <v>12.13302744219147</v>
+        <v>1.971616959356115</v>
       </c>
       <c r="E4" t="n">
-        <v>8.614494295719174</v>
+        <v>1.399855323054366</v>
       </c>
       <c r="F4" t="n">
-        <v>6.723054750622592</v>
+        <v>1.092496396976171</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.16487603759968</v>
+        <v>3.439292356109947</v>
       </c>
       <c r="D5" t="n">
-        <v>2.181511479122538</v>
+        <v>0.3544956153574125</v>
       </c>
       <c r="E5" t="n">
-        <v>8.614494295719174</v>
+        <v>1.399855323054366</v>
       </c>
       <c r="F5" t="n">
-        <v>6.723054750622592</v>
+        <v>1.092496396976171</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.21179508972256</v>
+        <v>5.071916702079916</v>
       </c>
       <c r="D6" t="n">
-        <v>20.64497773313087</v>
+        <v>3.354808881633766</v>
       </c>
       <c r="E6" t="n">
-        <v>8.614494295719174</v>
+        <v>1.399855323054366</v>
       </c>
       <c r="F6" t="n">
-        <v>6.723054750622592</v>
+        <v>1.092496396976171</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.68375449215327</v>
+        <v>4.823610104974906</v>
       </c>
       <c r="D7" t="n">
-        <v>19.27838390065789</v>
+        <v>3.132737383856906</v>
       </c>
       <c r="E7" t="n">
-        <v>8.614494295719174</v>
+        <v>1.399855323054366</v>
       </c>
       <c r="F7" t="n">
-        <v>6.723054750622592</v>
+        <v>1.092496396976171</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
